--- a/data/projects/56A0TXN/早期介入/交付预案/输出结果/维保SLA表.xlsx
+++ b/data/projects/56A0TXN/早期介入/交付预案/输出结果/维保SLA表.xlsx
@@ -489,7 +489,11 @@
           <t>热线受理</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -527,7 +531,11 @@
           <t>在线技术支持</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -565,7 +573,11 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -603,7 +615,11 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -641,7 +657,11 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -679,7 +699,11 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -717,7 +741,11 @@
           <t>现场问题处理</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -755,7 +783,11 @@
           <t>现场问题处理</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -793,7 +825,11 @@
           <t>现场问题处理</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -831,7 +867,11 @@
           <t>备件先行</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -869,7 +909,11 @@
           <t>备件先行</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -907,7 +951,11 @@
           <t>备件先行</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -945,7 +993,11 @@
           <t>现场硬件更换</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -983,7 +1035,11 @@
           <t>现场硬件更换</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1021,7 +1077,11 @@
           <t>现场硬件更换</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1059,7 +1119,11 @@
           <t>软件更新授权</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -2921,11 +2985,7 @@
           <t>热线受理</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -2963,11 +3023,7 @@
           <t>在线技术支持</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3005,11 +3061,7 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3047,11 +3099,7 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3089,11 +3137,7 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3131,11 +3175,7 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3173,11 +3213,7 @@
           <t>现场问题处理</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3215,11 +3251,7 @@
           <t>现场问题处理</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3257,11 +3289,7 @@
           <t>现场问题处理</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3299,11 +3327,7 @@
           <t>备件先行</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3341,11 +3365,7 @@
           <t>备件先行</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3383,11 +3403,7 @@
           <t>备件先行</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3425,11 +3441,7 @@
           <t>现场硬件更换</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3467,11 +3479,7 @@
           <t>现场硬件更换</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3509,11 +3517,7 @@
           <t>现场硬件更换</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3551,11 +3555,7 @@
           <t>软件更新授权</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
